--- a/5. SMS Reports/.Reports/12. Dec/SMS-NFSS 12.31.25 Financial Report_Final.xlsx
+++ b/5. SMS Reports/.Reports/12. Dec/SMS-NFSS 12.31.25 Financial Report_Final.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General Ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Month Statement" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Month Statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mm-yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm-yyyy"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -205,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -237,7 +236,7 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -402,6 +401,9 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -914,7 +916,7 @@
       <c r="C8" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -957,7 +959,7 @@
       <c r="C9" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1000,7 +1002,7 @@
       <c r="C10" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1043,7 +1045,7 @@
       <c r="C11" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1090,7 +1092,7 @@
       <c r="C12" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1137,7 +1139,7 @@
       <c r="C13" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1184,7 +1186,7 @@
       <c r="C14" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1231,7 +1233,7 @@
       <c r="C15" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1278,7 +1280,7 @@
       <c r="C16" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1321,7 +1323,7 @@
       <c r="C17" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1364,7 +1366,7 @@
       <c r="C18" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1407,7 +1409,7 @@
       <c r="C19" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1454,7 +1456,7 @@
       <c r="C20" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1497,7 +1499,7 @@
       <c r="C21" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1544,7 +1546,7 @@
       <c r="C22" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1591,7 +1593,7 @@
       <c r="C23" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1638,7 +1640,7 @@
       <c r="C24" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1685,7 +1687,7 @@
       <c r="C25" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1732,7 +1734,7 @@
       <c r="C26" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1779,7 +1781,7 @@
       <c r="C27" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1826,7 +1828,7 @@
       <c r="C28" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1873,7 +1875,7 @@
       <c r="C29" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1920,7 +1922,7 @@
       <c r="C30" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1967,7 +1969,7 @@
       <c r="C31" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2014,7 +2016,7 @@
       <c r="C32" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2061,7 +2063,7 @@
       <c r="C33" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2108,7 +2110,7 @@
       <c r="C34" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2155,7 +2157,7 @@
       <c r="C35" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2202,7 +2204,7 @@
       <c r="C36" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2249,7 +2251,7 @@
       <c r="C37" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2296,7 +2298,7 @@
       <c r="C38" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2343,7 +2345,7 @@
       <c r="C39" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2386,7 +2388,7 @@
       <c r="C40" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2429,7 +2431,7 @@
       <c r="C41" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2472,7 +2474,7 @@
       <c r="C42" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2515,7 +2517,7 @@
       <c r="C43" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2562,7 +2564,7 @@
       <c r="C44" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D44" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2609,7 +2611,7 @@
       <c r="C45" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2656,7 +2658,7 @@
       <c r="C46" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2703,7 +2705,7 @@
       <c r="C47" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2750,7 +2752,7 @@
       <c r="C48" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2793,7 +2795,7 @@
       <c r="C49" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2836,7 +2838,7 @@
       <c r="C50" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2883,7 +2885,7 @@
       <c r="C51" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2930,7 +2932,7 @@
       <c r="C52" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -3048,7 +3050,7 @@
       <c r="C56" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D56" s="11" t="n">
+      <c r="D56" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3162,7 +3164,7 @@
       <c r="C60" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D60" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3276,7 +3278,7 @@
       <c r="C64" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D64" s="11" t="n">
+      <c r="D64" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3319,7 +3321,7 @@
       <c r="C65" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D65" s="11" t="n">
+      <c r="D65" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3504,7 +3506,7 @@
       <c r="C72" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D72" s="11" t="n">
+      <c r="D72" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3551,7 +3553,7 @@
       <c r="C73" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3598,7 +3600,7 @@
       <c r="C74" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D74" s="11" t="n">
+      <c r="D74" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3645,7 +3647,7 @@
       <c r="C75" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D75" s="11" t="n">
+      <c r="D75" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -3692,7 +3694,7 @@
       <c r="C76" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D76" s="11" t="n">
+      <c r="D76" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3739,7 +3741,7 @@
       <c r="C77" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D77" s="11" t="n">
+      <c r="D77" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -3786,7 +3788,7 @@
       <c r="C78" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D78" s="11" t="n">
+      <c r="D78" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -3833,7 +3835,7 @@
       <c r="C79" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D79" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -3880,7 +3882,7 @@
       <c r="C80" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D80" s="11" t="n">
+      <c r="D80" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -3927,7 +3929,7 @@
       <c r="C81" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -3974,7 +3976,7 @@
       <c r="C82" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D82" s="11" t="n">
+      <c r="D82" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -4021,7 +4023,7 @@
       <c r="C83" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D83" s="11" t="n">
+      <c r="D83" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4068,7 +4070,7 @@
       <c r="C84" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D84" s="11" t="n">
+      <c r="D84" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4115,7 +4117,7 @@
       <c r="C85" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D85" s="11" t="n">
+      <c r="D85" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -4162,7 +4164,7 @@
       <c r="C86" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D86" s="11" t="n">
+      <c r="D86" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -4209,7 +4211,7 @@
       <c r="C87" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D87" s="11" t="n">
+      <c r="D87" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -4256,7 +4258,7 @@
       <c r="C88" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D88" s="11" t="n">
+      <c r="D88" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -4303,7 +4305,7 @@
       <c r="C89" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D89" s="11" t="n">
+      <c r="D89" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4350,7 +4352,7 @@
       <c r="C90" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D90" s="11" t="n">
+      <c r="D90" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -4397,7 +4399,7 @@
       <c r="C91" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D91" s="11" t="n">
+      <c r="D91" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -4444,7 +4446,7 @@
       <c r="C92" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D92" s="11" t="n">
+      <c r="D92" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E92" s="9" t="inlineStr">
@@ -4491,7 +4493,7 @@
       <c r="C93" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D93" s="11" t="n">
+      <c r="D93" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -4538,7 +4540,7 @@
       <c r="C94" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D94" s="11" t="n">
+      <c r="D94" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E94" s="9" t="inlineStr">
@@ -4585,7 +4587,7 @@
       <c r="C95" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D95" s="11" t="n">
+      <c r="D95" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -4632,7 +4634,7 @@
       <c r="C96" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D96" s="11" t="n">
+      <c r="D96" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -4679,7 +4681,7 @@
       <c r="C97" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D97" s="11" t="n">
+      <c r="D97" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -4726,7 +4728,7 @@
       <c r="C98" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D98" s="11" t="n">
+      <c r="D98" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4773,7 +4775,7 @@
       <c r="C99" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D99" s="11" t="n">
+      <c r="D99" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -4820,7 +4822,7 @@
       <c r="C100" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D100" s="11" t="n">
+      <c r="D100" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -4867,7 +4869,7 @@
       <c r="C101" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D101" s="11" t="n">
+      <c r="D101" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -4914,7 +4916,7 @@
       <c r="C102" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D102" s="11" t="n">
+      <c r="D102" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -4961,7 +4963,7 @@
       <c r="C103" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D103" s="11" t="n">
+      <c r="D103" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -5008,7 +5010,7 @@
       <c r="C104" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D104" s="11" t="n">
+      <c r="D104" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -5055,7 +5057,7 @@
       <c r="C105" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -5102,7 +5104,7 @@
       <c r="C106" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D106" s="11" t="n">
+      <c r="D106" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -5149,7 +5151,7 @@
       <c r="C107" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D107" s="11" t="n">
+      <c r="D107" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -5196,7 +5198,7 @@
       <c r="C108" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D108" s="11" t="n">
+      <c r="D108" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -5243,7 +5245,7 @@
       <c r="C109" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D109" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -5290,7 +5292,7 @@
       <c r="C110" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D110" s="11" t="n">
+      <c r="D110" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -5337,7 +5339,7 @@
       <c r="C111" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D111" s="11" t="n">
+      <c r="D111" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -5384,7 +5386,7 @@
       <c r="C112" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D112" s="11" t="n">
+      <c r="D112" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -5431,7 +5433,7 @@
       <c r="C113" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D113" s="11" t="n">
+      <c r="D113" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -5478,7 +5480,7 @@
       <c r="C114" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D114" s="11" t="n">
+      <c r="D114" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -5525,7 +5527,7 @@
       <c r="C115" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D115" s="11" t="n">
+      <c r="D115" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -5572,7 +5574,7 @@
       <c r="C116" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D116" s="11" t="n">
+      <c r="D116" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -5619,7 +5621,7 @@
       <c r="C117" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D117" s="11" t="n">
+      <c r="D117" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -5666,7 +5668,7 @@
       <c r="C118" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D118" s="11" t="n">
+      <c r="D118" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -5713,7 +5715,7 @@
       <c r="C119" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D119" s="11" t="n">
+      <c r="D119" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -5760,7 +5762,7 @@
       <c r="C120" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D120" s="11" t="n">
+      <c r="D120" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -5807,7 +5809,7 @@
       <c r="C121" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D121" s="11" t="n">
+      <c r="D121" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -5854,7 +5856,7 @@
       <c r="C122" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D122" s="11" t="n">
+      <c r="D122" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E122" s="9" t="inlineStr">
@@ -5901,7 +5903,7 @@
       <c r="C123" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D123" s="11" t="n">
+      <c r="D123" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -5948,7 +5950,7 @@
       <c r="C124" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D124" s="11" t="n">
+      <c r="D124" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E124" s="9" t="inlineStr">
@@ -5995,7 +5997,7 @@
       <c r="C125" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D125" s="11" t="n">
+      <c r="D125" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E125" s="9" t="inlineStr">
@@ -6042,7 +6044,7 @@
       <c r="C126" s="10" t="n">
         <v>46031</v>
       </c>
-      <c r="D126" s="11" t="n">
+      <c r="D126" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E126" s="9" t="inlineStr">
@@ -6160,7 +6162,7 @@
       <c r="C130" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D130" s="11" t="n">
+      <c r="D130" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E130" s="9" t="inlineStr">
@@ -6274,7 +6276,7 @@
       <c r="C134" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D134" s="11" t="n">
+      <c r="D134" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -6317,7 +6319,7 @@
       <c r="C135" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D135" s="11" t="n">
+      <c r="D135" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -6435,7 +6437,7 @@
       <c r="C139" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D139" s="11" t="n">
+      <c r="D139" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E139" s="9" t="inlineStr">
@@ -6549,7 +6551,7 @@
       <c r="C143" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D143" s="11" t="n">
+      <c r="D143" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -6592,7 +6594,7 @@
       <c r="C144" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D144" s="11" t="n">
+      <c r="D144" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -6639,7 +6641,7 @@
       <c r="C145" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D145" s="11" t="n">
+      <c r="D145" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -6682,7 +6684,7 @@
       <c r="C146" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D146" s="11" t="n">
+      <c r="D146" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E146" s="9" t="inlineStr">
@@ -6729,7 +6731,7 @@
       <c r="C147" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D147" s="11" t="n">
+      <c r="D147" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -6772,7 +6774,7 @@
       <c r="C148" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D148" s="11" t="n">
+      <c r="D148" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E148" s="9" t="inlineStr">
@@ -6886,7 +6888,7 @@
       <c r="C152" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D152" s="11" t="n">
+      <c r="D152" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E152" s="9" t="inlineStr">
@@ -7213,7 +7215,7 @@
       <c r="C165" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D165" s="11" t="n">
+      <c r="D165" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E165" s="9" t="inlineStr">
@@ -7256,7 +7258,7 @@
       <c r="C166" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D166" s="11" t="n">
+      <c r="D166" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E166" s="9" t="inlineStr">
@@ -7299,7 +7301,7 @@
       <c r="C167" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D167" s="11" t="n">
+      <c r="D167" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E167" s="9" t="inlineStr">
@@ -7342,7 +7344,7 @@
       <c r="C168" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D168" s="11" t="n">
+      <c r="D168" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E168" s="9" t="inlineStr">
@@ -7385,7 +7387,7 @@
       <c r="C169" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D169" s="11" t="n">
+      <c r="D169" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E169" s="9" t="inlineStr">
@@ -7428,7 +7430,7 @@
       <c r="C170" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D170" s="11" t="n">
+      <c r="D170" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E170" s="9" t="inlineStr">
@@ -7471,7 +7473,7 @@
       <c r="C171" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D171" s="11" t="n">
+      <c r="D171" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E171" s="9" t="inlineStr">
@@ -7514,7 +7516,7 @@
       <c r="C172" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D172" s="11" t="n">
+      <c r="D172" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E172" s="9" t="inlineStr">
@@ -7628,7 +7630,7 @@
       <c r="C176" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D176" s="11" t="n">
+      <c r="D176" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E176" s="9" t="inlineStr">
@@ -7813,7 +7815,7 @@
       <c r="C183" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D183" s="11" t="n">
+      <c r="D183" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E183" s="9" t="inlineStr">
@@ -7927,7 +7929,7 @@
       <c r="C187" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D187" s="11" t="n">
+      <c r="D187" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E187" s="9" t="inlineStr">
@@ -7970,7 +7972,7 @@
       <c r="C188" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D188" s="11" t="n">
+      <c r="D188" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E188" s="9" t="inlineStr">
@@ -8013,7 +8015,7 @@
       <c r="C189" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D189" s="11" t="n">
+      <c r="D189" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E189" s="9" t="inlineStr">
@@ -8056,7 +8058,7 @@
       <c r="C190" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D190" s="11" t="n">
+      <c r="D190" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E190" s="9" t="inlineStr">
@@ -8099,7 +8101,7 @@
       <c r="C191" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D191" s="11" t="n">
+      <c r="D191" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E191" s="9" t="inlineStr">
@@ -8142,7 +8144,7 @@
       <c r="C192" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D192" s="11" t="n">
+      <c r="D192" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E192" s="9" t="inlineStr">
@@ -8260,7 +8262,7 @@
       <c r="C196" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D196" s="11" t="n">
+      <c r="D196" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E196" s="9" t="inlineStr">
@@ -8303,7 +8305,7 @@
       <c r="C197" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D197" s="11" t="n">
+      <c r="D197" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E197" s="9" t="inlineStr">
@@ -8492,7 +8494,7 @@
       <c r="C204" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D204" s="11" t="n">
+      <c r="D204" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E204" s="9" t="inlineStr">
@@ -8535,7 +8537,7 @@
       <c r="C205" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D205" s="11" t="n">
+      <c r="D205" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E205" s="9" t="inlineStr">
@@ -8653,7 +8655,7 @@
       <c r="C209" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D209" s="11" t="n">
+      <c r="D209" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E209" s="9" t="inlineStr">
@@ -8696,7 +8698,7 @@
       <c r="C210" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D210" s="11" t="n">
+      <c r="D210" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E210" s="9" t="inlineStr">
@@ -8952,7 +8954,7 @@
       <c r="C220" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D220" s="11" t="n">
+      <c r="D220" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E220" s="9" t="inlineStr">
@@ -8999,7 +9001,7 @@
       <c r="C221" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D221" s="11" t="n">
+      <c r="D221" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E221" s="9" t="inlineStr">
@@ -9046,7 +9048,7 @@
       <c r="C222" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D222" s="11" t="n">
+      <c r="D222" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E222" s="9" t="inlineStr">
@@ -9093,7 +9095,7 @@
       <c r="C223" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D223" s="11" t="n">
+      <c r="D223" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E223" s="9" t="inlineStr">
@@ -9140,7 +9142,7 @@
       <c r="C224" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D224" s="11" t="n">
+      <c r="D224" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E224" s="9" t="inlineStr">
@@ -9183,7 +9185,7 @@
       <c r="C225" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D225" s="11" t="n">
+      <c r="D225" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E225" s="9" t="inlineStr">
@@ -9581,7 +9583,7 @@
       <c r="C241" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D241" s="11" t="n">
+      <c r="D241" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E241" s="9" t="inlineStr">
@@ -9770,7 +9772,7 @@
       <c r="C248" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D248" s="11" t="n">
+      <c r="D248" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E248" s="9" t="inlineStr">
@@ -9888,7 +9890,7 @@
       <c r="C252" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D252" s="11" t="n">
+      <c r="D252" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E252" s="9" t="inlineStr">
@@ -10077,7 +10079,7 @@
       <c r="C259" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D259" s="11" t="n">
+      <c r="D259" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E259" s="9" t="inlineStr">
@@ -10195,7 +10197,7 @@
       <c r="C263" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D263" s="11" t="n">
+      <c r="D263" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E263" s="9" t="inlineStr">
@@ -10384,7 +10386,7 @@
       <c r="C270" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D270" s="11" t="n">
+      <c r="D270" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E270" s="9" t="inlineStr">
@@ -10569,7 +10571,7 @@
       <c r="C277" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D277" s="11" t="n">
+      <c r="D277" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E277" s="9" t="inlineStr">
@@ -10616,7 +10618,7 @@
       <c r="C278" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D278" s="11" t="n">
+      <c r="D278" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E278" s="9" t="inlineStr">
@@ -10663,7 +10665,7 @@
       <c r="C279" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D279" s="11" t="n">
+      <c r="D279" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E279" s="9" t="inlineStr">
@@ -10706,7 +10708,7 @@
       <c r="C280" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D280" s="11" t="n">
+      <c r="D280" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E280" s="9" t="inlineStr">
@@ -10753,7 +10755,7 @@
       <c r="C281" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D281" s="11" t="n">
+      <c r="D281" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E281" s="9" t="inlineStr">
@@ -10871,7 +10873,7 @@
       <c r="C285" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D285" s="11" t="n">
+      <c r="D285" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E285" s="9" t="inlineStr">
@@ -10985,7 +10987,7 @@
       <c r="C289" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D289" s="11" t="n">
+      <c r="D289" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E289" s="9" t="inlineStr">
@@ -11312,7 +11314,7 @@
       <c r="C302" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D302" s="11" t="n">
+      <c r="D302" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E302" s="9" t="inlineStr">
@@ -11359,7 +11361,7 @@
       <c r="C303" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D303" s="11" t="n">
+      <c r="D303" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E303" s="9" t="inlineStr">
@@ -11406,7 +11408,7 @@
       <c r="C304" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D304" s="11" t="n">
+      <c r="D304" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E304" s="9" t="inlineStr">
@@ -11453,7 +11455,7 @@
       <c r="C305" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D305" s="11" t="n">
+      <c r="D305" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E305" s="9" t="inlineStr">
@@ -11571,7 +11573,7 @@
       <c r="C309" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D309" s="11" t="n">
+      <c r="D309" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E309" s="9" t="inlineStr">
@@ -11689,7 +11691,7 @@
       <c r="C313" s="10" t="n">
         <v>46031</v>
       </c>
-      <c r="D313" s="11" t="n">
+      <c r="D313" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E313" s="9" t="inlineStr">
@@ -11807,7 +11809,7 @@
       <c r="C317" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D317" s="11" t="n">
+      <c r="D317" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E317" s="9" t="inlineStr">
@@ -11854,7 +11856,7 @@
       <c r="C318" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D318" s="11" t="n">
+      <c r="D318" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E318" s="9" t="inlineStr">
@@ -11897,7 +11899,7 @@
       <c r="C319" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D319" s="11" t="n">
+      <c r="D319" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E319" s="9" t="inlineStr">
@@ -12015,7 +12017,7 @@
       <c r="C323" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D323" s="11" t="n">
+      <c r="D323" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E323" s="9" t="inlineStr">
@@ -12120,2368 +12122,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F119"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11.4285714285714" customWidth="1" min="1" max="1"/>
-    <col width="37.1428571428571" customWidth="1" min="2" max="2"/>
-    <col width="17.1428571428571" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Storsafe Management Solutions - NFSS (sms-nfss)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Cash Flow Statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Period = Jan 2025-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Book = Accrual ; Tree = ysi_cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="24" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Period to Date</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Year to Date</t>
-        </is>
-      </c>
-      <c r="F5" s="24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>4000-0000</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> INCOME</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="28" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="28" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="28" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>4100-0000</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RENT INCOME</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>4500-1001</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Storage Rent</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>112669.34</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>112669.34</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>4710-0000</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Less: Concessions</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>-5632.85</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>-5632.85</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>4990-0000</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            NET RENT INCOME</t>
-        </is>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>107036.49</v>
-      </c>
-      <c r="D11" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>107036.49</v>
-      </c>
-      <c r="F11" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>5000-0001</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Merchandise Income</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>499.75</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>499.75</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>5000-0002</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Merchandise COGS</t>
-        </is>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>-893.09</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>-893.09</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>5000-0003</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Net Merchandise Sales</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>-393.34</v>
-      </c>
-      <c r="D14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>-393.34</v>
-      </c>
-      <c r="F14" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>5000-0010</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Tenant Protection Income</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>4058.48</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>4058.48</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>5000-0011</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Tenant Protection COGS</t>
-        </is>
-      </c>
-      <c r="C16" s="29" t="n">
-        <v>-694.13</v>
-      </c>
-      <c r="D16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="29" t="n">
-        <v>-694.13</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>5000-0012</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Net Tenant Protection Income</t>
-        </is>
-      </c>
-      <c r="C17" s="30" t="n">
-        <v>3364.35</v>
-      </c>
-      <c r="D17" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="30" t="n">
-        <v>3364.35</v>
-      </c>
-      <c r="F17" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>5000-0013</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Phone Convenience Fee</t>
-        </is>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>5000-1000</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL ANCILLARY INCOME</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="n">
-        <v>2978.01</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>2978.01</v>
-      </c>
-      <c r="F19" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="28" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>5600-0000</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    OTHER INCOME</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>5700-0000</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Miscellaneous Income</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>5800-0000</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Late Fee</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>1242</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>1242</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>5805-0000</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Administrative Fee</t>
-        </is>
-      </c>
-      <c r="C24" s="29" t="n">
-        <v>763</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>763</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>5890-0000</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL OTHER INCOME</t>
-        </is>
-      </c>
-      <c r="C25" s="30" t="n">
-        <v>8005</v>
-      </c>
-      <c r="D25" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="30" t="n">
-        <v>8005</v>
-      </c>
-      <c r="F25" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="28" t="n"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>5990-0000</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                TOTAL INCOME</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="n">
-        <v>118019.5</v>
-      </c>
-      <c r="D27" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="34" t="n">
-        <v>118019.5</v>
-      </c>
-      <c r="F27" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
-      <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>6000-0000</t>
-        </is>
-      </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> EXPENSES</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="n"/>
-      <c r="D29" s="35" t="n"/>
-      <c r="E29" s="35" t="n"/>
-      <c r="F29" s="35" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="28" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>6050-0000</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ADVERTISING and MARKETING</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>6050-0010</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Advertising</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>284.1</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>284.1</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>6050-0025</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Internet Marketing</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>12546.5</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>12546.5</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>6050-0030</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Marketing Other</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="29" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="F34" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>6050-9999</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            ADVERTISING and MARKETING TOTAL</t>
-        </is>
-      </c>
-      <c r="C35" s="30" t="n">
-        <v>12862.65</v>
-      </c>
-      <c r="D35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="30" t="n">
-        <v>12862.65</v>
-      </c>
-      <c r="F35" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="28" t="n"/>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="28" t="n"/>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="28" t="n"/>
-      <c r="F36" s="28" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>6100-0000</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REPAIRS AND MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>6110-1050</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Repairs and  Maintenance</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>680</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>680</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>6110-1060</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Maintenance Tools and Supplies</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>96.73999999999999</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>96.73999999999999</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>6110-1175</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Extermination</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="n">
-        <v>840</v>
-      </c>
-      <c r="D40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="29" t="n">
-        <v>840</v>
-      </c>
-      <c r="F40" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="28" t="inlineStr">
-        <is>
-          <t>6199-9999</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL REPAIRS AND MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C41" s="30" t="n">
-        <v>1616.74</v>
-      </c>
-      <c r="D41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="30" t="n">
-        <v>1616.74</v>
-      </c>
-      <c r="F41" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="28" t="n"/>
-      <c r="D42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
-        <is>
-          <t>6200-0000</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    GROUNDS</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
-        <is>
-          <t>6200-0001</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Trash Disposal</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="n">
-        <v>1665.02</v>
-      </c>
-      <c r="D44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>1665.02</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="28" t="inlineStr">
-        <is>
-          <t>6200-0015</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Snow Removal</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D45" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="29" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F45" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>6299-9999</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL GROUNDS</t>
-        </is>
-      </c>
-      <c r="C46" s="30" t="n">
-        <v>3065.02</v>
-      </c>
-      <c r="D46" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="30" t="n">
-        <v>3065.02</v>
-      </c>
-      <c r="F46" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="28" t="n"/>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="28" t="n"/>
-      <c r="D47" s="28" t="n"/>
-      <c r="E47" s="28" t="n"/>
-      <c r="F47" s="28" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>6400-0000</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    UTILITIES</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n"/>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="28" t="inlineStr">
-        <is>
-          <t>6400-0010</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Electricity</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="n">
-        <v>431.37</v>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="12" t="n">
-        <v>431.37</v>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>6400-0046</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Internet Services</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="n">
-        <v>1243.5</v>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>1243.5</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="inlineStr">
-        <is>
-          <t>6400-0047</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Telephone Service</t>
-        </is>
-      </c>
-      <c r="C51" s="29" t="n">
-        <v>146.4</v>
-      </c>
-      <c r="D51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="29" t="n">
-        <v>146.4</v>
-      </c>
-      <c r="F51" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>6425-0000</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL UTILITIES</t>
-        </is>
-      </c>
-      <c r="C52" s="30" t="n">
-        <v>1821.27</v>
-      </c>
-      <c r="D52" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="30" t="n">
-        <v>1821.27</v>
-      </c>
-      <c r="F52" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="28" t="inlineStr">
-        <is>
-          <t>6450-0010</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Management Fee</t>
-        </is>
-      </c>
-      <c r="C53" s="29" t="n">
-        <v>5431.34</v>
-      </c>
-      <c r="D53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="29" t="n">
-        <v>5431.34</v>
-      </c>
-      <c r="F53" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>6455-0000</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL ADMINISTRATIVE &amp; MANAGEMENT EXPENSES</t>
-        </is>
-      </c>
-      <c r="C54" s="30" t="n">
-        <v>5431.34</v>
-      </c>
-      <c r="D54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="30" t="n">
-        <v>5431.34</v>
-      </c>
-      <c r="F54" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>6461-0000</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Property Tax</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="n">
-        <v>37140</v>
-      </c>
-      <c r="D55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="12" t="n">
-        <v>37140</v>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="28" t="inlineStr">
-        <is>
-          <t>6461-1000</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Property Insurance</t>
-        </is>
-      </c>
-      <c r="C56" s="29" t="n">
-        <v>6461.75</v>
-      </c>
-      <c r="D56" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="29" t="n">
-        <v>6461.75</v>
-      </c>
-      <c r="F56" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="28" t="inlineStr">
-        <is>
-          <t>6470-0000</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PROPERTY TAXES &amp; INSURANCE</t>
-        </is>
-      </c>
-      <c r="C57" s="30" t="n">
-        <v>43601.75</v>
-      </c>
-      <c r="D57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="30" t="n">
-        <v>43601.75</v>
-      </c>
-      <c r="F57" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="28" t="inlineStr">
-        <is>
-          <t>7000-0008</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Meeting Meals</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="n">
-        <v>30.74</v>
-      </c>
-      <c r="D58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="12" t="n">
-        <v>30.74</v>
-      </c>
-      <c r="F58" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="28" t="inlineStr">
-        <is>
-          <t>7000-0013</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Vehicle Expense</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="n">
-        <v>66.15000000000001</v>
-      </c>
-      <c r="D59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="12" t="n">
-        <v>66.15000000000001</v>
-      </c>
-      <c r="F59" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="28" t="inlineStr">
-        <is>
-          <t>7000-0026</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Software</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="n">
-        <v>3203.42</v>
-      </c>
-      <c r="D60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="12" t="n">
-        <v>3203.42</v>
-      </c>
-      <c r="F60" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>7000-0045</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Bank Charges Expense</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="n">
-        <v>2366.17</v>
-      </c>
-      <c r="D61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="12" t="n">
-        <v>2366.17</v>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>7000-0047</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Credit Card Processing Fees</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="n">
-        <v>3750.64</v>
-      </c>
-      <c r="D62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="12" t="n">
-        <v>3750.64</v>
-      </c>
-      <c r="F62" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="28" t="inlineStr">
-        <is>
-          <t>7000-0050</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Postage and Shipping Fees</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="D63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="12" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>7000-0054</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Travel Expenses</t>
-        </is>
-      </c>
-      <c r="C64" s="29" t="n">
-        <v>150.31</v>
-      </c>
-      <c r="D64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="29" t="n">
-        <v>150.31</v>
-      </c>
-      <c r="F64" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="28" t="inlineStr">
-        <is>
-          <t>7000-1000</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL G and A EXPENSE</t>
-        </is>
-      </c>
-      <c r="C65" s="30" t="n">
-        <v>9570.5</v>
-      </c>
-      <c r="D65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="30" t="n">
-        <v>9570.5</v>
-      </c>
-      <c r="F65" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="28" t="n"/>
-      <c r="B66" s="9" t="n"/>
-      <c r="C66" s="28" t="n"/>
-      <c r="D66" s="28" t="n"/>
-      <c r="E66" s="28" t="n"/>
-      <c r="F66" s="28" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>7200-0000</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    PROFESSIONAL FEES</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>7200-0001</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Answering Service</t>
-        </is>
-      </c>
-      <c r="C68" s="12" t="n">
-        <v>-117.06</v>
-      </c>
-      <c r="D68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="12" t="n">
-        <v>-117.06</v>
-      </c>
-      <c r="F68" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>7200-0002</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Communication Center</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="n">
-        <v>7863.35</v>
-      </c>
-      <c r="D69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="12" t="n">
-        <v>7863.35</v>
-      </c>
-      <c r="F69" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>7200-0003</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Auction Costs</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="n">
-        <v>1319.27</v>
-      </c>
-      <c r="D70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="12" t="n">
-        <v>1319.27</v>
-      </c>
-      <c r="F70" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>7200-0020</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Professional Fees</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="n">
-        <v>182</v>
-      </c>
-      <c r="D71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="29" t="n">
-        <v>182</v>
-      </c>
-      <c r="F71" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>7200-0100</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PROFESSIONAL FEES</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="n">
-        <v>9247.559999999999</v>
-      </c>
-      <c r="D72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="30" t="n">
-        <v>9247.559999999999</v>
-      </c>
-      <c r="F72" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="28" t="n"/>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="28" t="n"/>
-      <c r="D73" s="28" t="n"/>
-      <c r="E73" s="28" t="n"/>
-      <c r="F73" s="28" t="n"/>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>7310-0000</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SUPERVISORY PAYROLL</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="28" t="inlineStr">
-        <is>
-          <t>7310-0005</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Supervisory Payroll Expense</t>
-        </is>
-      </c>
-      <c r="C75" s="29" t="n">
-        <v>2413.24</v>
-      </c>
-      <c r="D75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="29" t="n">
-        <v>2413.24</v>
-      </c>
-      <c r="F75" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>7310-0100</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL SUPERVISORY PAYROLL</t>
-        </is>
-      </c>
-      <c r="C76" s="36" t="n">
-        <v>2413.24</v>
-      </c>
-      <c r="D76" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="36" t="n">
-        <v>2413.24</v>
-      </c>
-      <c r="F76" s="36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>7500-0000</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PAYROLL</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="n">
-        <v>2413.24</v>
-      </c>
-      <c r="D77" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="30" t="n">
-        <v>2413.24</v>
-      </c>
-      <c r="F77" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="28" t="n"/>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="31" t="n"/>
-      <c r="D78" s="31" t="n"/>
-      <c r="E78" s="31" t="n"/>
-      <c r="F78" s="31" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="32" t="inlineStr">
-        <is>
-          <t>7999-9000</t>
-        </is>
-      </c>
-      <c r="B79" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL NET OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="C79" s="34" t="n">
-        <v>89630.07000000001</v>
-      </c>
-      <c r="D79" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="34" t="n">
-        <v>89630.07000000001</v>
-      </c>
-      <c r="F79" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="28" t="n"/>
-      <c r="B80" s="9" t="n"/>
-      <c r="C80" s="37" t="n"/>
-      <c r="D80" s="37" t="n"/>
-      <c r="E80" s="37" t="n"/>
-      <c r="F80" s="37" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="38" t="inlineStr">
-        <is>
-          <t>7999-9999</t>
-        </is>
-      </c>
-      <c r="B81" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NET OPERATING INCOME</t>
-        </is>
-      </c>
-      <c r="C81" s="40" t="n">
-        <v>28389.43</v>
-      </c>
-      <c r="D81" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="40" t="n">
-        <v>28389.43</v>
-      </c>
-      <c r="F81" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="28" t="inlineStr">
-        <is>
-          <t>8540-0000</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Loan Interest</t>
-        </is>
-      </c>
-      <c r="C82" s="41" t="n">
-        <v>35922.84</v>
-      </c>
-      <c r="D82" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="41" t="n">
-        <v>35922.84</v>
-      </c>
-      <c r="F82" s="41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="28" t="inlineStr">
-        <is>
-          <t>8590-0000</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL LOAN INTEREST</t>
-        </is>
-      </c>
-      <c r="C83" s="30" t="n">
-        <v>35922.84</v>
-      </c>
-      <c r="D83" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="30" t="n">
-        <v>35922.84</v>
-      </c>
-      <c r="F83" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="28" t="n"/>
-      <c r="B84" s="9" t="n"/>
-      <c r="C84" s="31" t="n"/>
-      <c r="D84" s="31" t="n"/>
-      <c r="E84" s="31" t="n"/>
-      <c r="F84" s="31" t="n"/>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="32" t="inlineStr">
-        <is>
-          <t>8990-0000</t>
-        </is>
-      </c>
-      <c r="B85" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="C85" s="34" t="n">
-        <v>35922.84</v>
-      </c>
-      <c r="D85" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="34" t="n">
-        <v>35922.84</v>
-      </c>
-      <c r="F85" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="28" t="n"/>
-      <c r="B86" s="9" t="n"/>
-      <c r="C86" s="37" t="n"/>
-      <c r="D86" s="37" t="n"/>
-      <c r="E86" s="37" t="n"/>
-      <c r="F86" s="37" t="n"/>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="32" t="inlineStr">
-        <is>
-          <t>9090-0000</t>
-        </is>
-      </c>
-      <c r="B87" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NET INCOME</t>
-        </is>
-      </c>
-      <c r="C87" s="42" t="n">
-        <v>-7533.41</v>
-      </c>
-      <c r="D87" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="42" t="n">
-        <v>-7533.41</v>
-      </c>
-      <c r="F87" s="42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="28" t="n"/>
-      <c r="B88" s="9" t="n"/>
-      <c r="C88" s="43" t="n"/>
-      <c r="D88" s="43" t="n"/>
-      <c r="E88" s="43" t="n"/>
-      <c r="F88" s="43" t="n"/>
-    </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="28" t="n"/>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="n"/>
-      <c r="D89" s="18" t="n"/>
-      <c r="E89" s="18" t="n"/>
-      <c r="F89" s="18" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="28" t="n"/>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="28" t="n"/>
-      <c r="D90" s="28" t="n"/>
-      <c r="E90" s="28" t="n"/>
-      <c r="F90" s="28" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="28" t="inlineStr">
-        <is>
-          <t>1300-0000</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="n">
-        <v>-8332.23</v>
-      </c>
-      <c r="D91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>-8332.23</v>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="28" t="inlineStr">
-        <is>
-          <t>1350-0001</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Pre-Paid Insurance</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>1815.75</v>
-      </c>
-      <c r="D92" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>1815.75</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="28" t="inlineStr">
-        <is>
-          <t>2110-0000</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Note 1 Principal</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>-6481.2</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>-6481.2</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="28" t="inlineStr">
-        <is>
-          <t>2150-0020</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Due To/(From) Other Property</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>6895.35</v>
-      </c>
-      <c r="D94" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="12" t="n">
-        <v>6895.35</v>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="28" t="inlineStr">
-        <is>
-          <t>2150-0022</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Due To/(From) SSSM</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>2650</v>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>2650</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="28" t="inlineStr">
-        <is>
-          <t>2200-0000</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>20959.96</v>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>20959.96</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="28" t="inlineStr">
-        <is>
-          <t>2210-0000</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Prepaid Rent</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>-501.99</v>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>-501.99</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="28" t="inlineStr">
-        <is>
-          <t>2305-0000</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Real Estate Tax Accrual</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="n">
-        <v>-18545.65</v>
-      </c>
-      <c r="D98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>-18545.65</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="28" t="inlineStr">
-        <is>
-          <t>2310-0000</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Sales Tax Collected</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
-        <v>-89.77</v>
-      </c>
-      <c r="D99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>-89.77</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="28" t="inlineStr">
-        <is>
-          <t>2640-0998</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Expense Accrual</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="28" t="inlineStr">
-        <is>
-          <t>2640-0999</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Payroll Accrual</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="D101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="28" t="inlineStr">
-        <is>
-          <t>3300-0000</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Owner Distributions</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="n">
-        <v>-9638.67</v>
-      </c>
-      <c r="D102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>-9638.67</v>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="28" t="inlineStr">
-        <is>
-          <t>7200-0003</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Auction Costs</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>-1319.27</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>-1319.27</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="28" t="n"/>
-      <c r="B104" s="9" t="n"/>
-      <c r="C104" s="31" t="n"/>
-      <c r="D104" s="31" t="n"/>
-      <c r="E104" s="31" t="n"/>
-      <c r="F104" s="31" t="n"/>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="28" t="n"/>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="C105" s="30" t="n">
-        <v>-12364.72</v>
-      </c>
-      <c r="D105" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="30" t="n">
-        <v>-12364.72</v>
-      </c>
-      <c r="F105" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="28" t="n"/>
-      <c r="B106" s="9" t="n"/>
-      <c r="C106" s="31" t="n"/>
-      <c r="D106" s="31" t="n"/>
-      <c r="E106" s="31" t="n"/>
-      <c r="F106" s="31" t="n"/>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="28" t="n"/>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    CASH FLOW</t>
-        </is>
-      </c>
-      <c r="C107" s="30" t="n">
-        <v>-19898.13</v>
-      </c>
-      <c r="D107" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="30" t="n">
-        <v>-19898.13</v>
-      </c>
-      <c r="F107" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="28" t="n"/>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="28" t="n"/>
-      <c r="B109" s="33" t="inlineStr">
-        <is>
-          <t>Period to Date</t>
-        </is>
-      </c>
-      <c r="C109" s="32" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="D109" s="32" t="inlineStr">
-        <is>
-          <t>Ending Balance</t>
-        </is>
-      </c>
-      <c r="E109" s="32" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="F109" s="28" t="n"/>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="28" t="inlineStr">
-        <is>
-          <t>1110-1532</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>EP NFSS Amalgamated</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="28" t="n"/>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="28" t="inlineStr">
-        <is>
-          <t>1110-4953</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>NFSS Chase</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="28" t="n"/>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="28" t="inlineStr">
-        <is>
-          <t>1110-4983</t>
-        </is>
-      </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>SMS NFSS Chase</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="n">
-        <v>15797.57</v>
-      </c>
-      <c r="D112" s="12" t="n">
-        <v>-2781.29</v>
-      </c>
-      <c r="E112" s="12" t="n">
-        <v>-18578.86</v>
-      </c>
-      <c r="F112" s="28" t="n"/>
-    </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="28" t="n"/>
-      <c r="B113" s="33" t="inlineStr">
-        <is>
-          <t>Total Cash</t>
-        </is>
-      </c>
-      <c r="C113" s="44" t="n">
-        <v>15797.57</v>
-      </c>
-      <c r="D113" s="44" t="n">
-        <v>-2781.29</v>
-      </c>
-      <c r="E113" s="44" t="n">
-        <v>-18578.86</v>
-      </c>
-      <c r="F113" s="28" t="n"/>
-    </row>
-    <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="28" t="n"/>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="28" t="n"/>
-      <c r="B115" s="33" t="inlineStr">
-        <is>
-          <t>Year to Date</t>
-        </is>
-      </c>
-      <c r="C115" s="32" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="D115" s="32" t="inlineStr">
-        <is>
-          <t>Ending Balance</t>
-        </is>
-      </c>
-      <c r="E115" s="32" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="F115" s="28" t="n"/>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="28" t="inlineStr">
-        <is>
-          <t>1110-1532</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>EP NFSS Amalgamated</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="28" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="28" t="inlineStr">
-        <is>
-          <t>1110-4953</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>NFSS Chase</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="28" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="28" t="inlineStr">
-        <is>
-          <t>1110-4983</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>SMS NFSS Chase</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="n">
-        <v>15797.57</v>
-      </c>
-      <c r="D118" s="12" t="n">
-        <v>-2781.29</v>
-      </c>
-      <c r="E118" s="12" t="n">
-        <v>-18578.86</v>
-      </c>
-      <c r="F118" s="28" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="28" t="n"/>
-      <c r="B119" s="33" t="inlineStr">
-        <is>
-          <t>Total Cash</t>
-        </is>
-      </c>
-      <c r="C119" s="44" t="n">
-        <v>15797.57</v>
-      </c>
-      <c r="D119" s="44" t="n">
-        <v>-2781.29</v>
-      </c>
-      <c r="E119" s="44" t="n">
-        <v>-18578.86</v>
-      </c>
-      <c r="F119" s="28" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A108:F108"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A114:F114"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="990" firstPageNumber="1" useFirstPageNumber="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18110,4 +15750,2333 @@
   <pageMargins left="0.7" right="0.7" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="5" fitToHeight="990" firstPageNumber="1" useFirstPageNumber="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F118"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="12.75"/>
+  <cols>
+    <col width="11.4285714285714" customWidth="1" min="1" max="1"/>
+    <col width="37.1428571428571" customWidth="1" min="2" max="2"/>
+    <col width="17.1428571428571" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Storsafe Management Solutions - NFSS (sms-nfss)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cash Flow Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Period = Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Book = Accrual ; Tree = ysi_cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="24" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Period to Date</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Year to Date</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>4000-0000</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> INCOME</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="27" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>4100-0000</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RENT INCOME</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>4500-1001</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Storage Rent</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>9798.58</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>112669.34</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>4710-0000</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Less: Concessions</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>-355</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>-5632.85</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>4990-0000</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            NET RENT INCOME</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>9443.58</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>107036.49</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>5000-0001</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Merchandise Income</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>499.75</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>5000-0002</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Merchandise COGS</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>-893.09</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>5000-0003</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Net Merchandise Sales</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>-393.34</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>5000-0010</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Tenant Protection Income</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>336</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>4058.48</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>5000-0011</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Tenant Protection COGS</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>-53</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>-694.13</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>5000-0012</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Net Tenant Protection Income</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>283</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>3364.35</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>5000-0013</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Phone Convenience Fee</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>5000-1000</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL ANCILLARY INCOME</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>183</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>2978.01</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>5600-0000</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>5700-0000</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Miscellaneous Income</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>5800-0000</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Late Fee</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>5805-0000</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Administrative Fee</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="29" t="n">
+        <v>763</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>5890-0000</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>2059</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>8005</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="28" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>5990-0000</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="n">
+        <v>11685.58</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>118019.5</v>
+      </c>
+      <c r="F27" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>6000-0000</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> EXPENSES</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="35" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>6050-0000</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADVERTISING and MARKETING</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>6050-0010</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Advertising</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>6050-0025</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Internet Marketing</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>1183.27</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>12546.5</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>6050-0030</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Marketing Other</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>6050-9999</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            ADVERTISING and MARKETING TOTAL</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>1183.27</v>
+      </c>
+      <c r="D35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>12862.65</v>
+      </c>
+      <c r="F35" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="28" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>6100-0000</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REPAIRS AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>6110-1050</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Repairs and  Maintenance</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>680</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>6110-1060</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Maintenance Tools and Supplies</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>96.73999999999999</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>6110-1175</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Extermination</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>840</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>6199-9999</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL REPAIRS AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <v>1616.74</v>
+      </c>
+      <c r="F41" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="28" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>6200-0000</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUNDS</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>6200-0001</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Trash Disposal</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>1665.02</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>6200-0015</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Snow Removal</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="29" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F45" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>6299-9999</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL GROUNDS</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>3065.02</v>
+      </c>
+      <c r="F46" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="28" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>6400-0000</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UTILITIES</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>6400-0010</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Electricity</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>431.37</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>6400-0046</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Internet Services</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>1243.5</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>6400-0047</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Telephone Service</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="29" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="F51" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>6425-0000</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL UTILITIES</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="n">
+        <v>144.63</v>
+      </c>
+      <c r="D52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>1821.27</v>
+      </c>
+      <c r="F52" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>6450-0010</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Management Fee</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="n">
+        <v>530.05</v>
+      </c>
+      <c r="D53" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="29" t="n">
+        <v>5431.34</v>
+      </c>
+      <c r="F53" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>6455-0000</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL ADMINISTRATIVE &amp; MANAGEMENT EXPENSES</t>
+        </is>
+      </c>
+      <c r="C54" s="30" t="n">
+        <v>530.05</v>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="30" t="n">
+        <v>5431.34</v>
+      </c>
+      <c r="F54" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>6461-0000</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Property Tax</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>37140</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>6461-1000</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Property Insurance</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="29" t="n">
+        <v>6461.75</v>
+      </c>
+      <c r="F56" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>6470-0000</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PROPERTY TAXES &amp; INSURANCE</t>
+        </is>
+      </c>
+      <c r="C57" s="30" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="30" t="n">
+        <v>43601.75</v>
+      </c>
+      <c r="F57" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>7000-0008</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Meeting Meals</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>7000-0013</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Vehicle Expense</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>7000-0026</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Software</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>3203.42</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>7000-0045</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Bank Charges Expense</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="n">
+        <v>232.33</v>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>2366.17</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>7000-0047</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Credit Card Processing Fees</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>3750.64</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>7000-0050</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Postage and Shipping Fees</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>7000-0054</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Travel Expenses</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="29" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="F64" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>7000-1000</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL G and A EXPENSE</t>
+        </is>
+      </c>
+      <c r="C65" s="30" t="n">
+        <v>967.87</v>
+      </c>
+      <c r="D65" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="30" t="n">
+        <v>9570.5</v>
+      </c>
+      <c r="F65" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="28" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="28" t="n"/>
+      <c r="D66" s="28" t="n"/>
+      <c r="E66" s="28" t="n"/>
+      <c r="F66" s="28" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>7200-0000</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PROFESSIONAL FEES</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>7200-0001</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Answering Service</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>-117.06</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>7200-0002</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Communication Center</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="n">
+        <v>626.95</v>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>7863.35</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>7200-0003</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Auction Costs</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>1319.27</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>7200-0020</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Professional Fees</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="D71" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="29" t="n">
+        <v>182</v>
+      </c>
+      <c r="F71" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>7200-0100</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PROFESSIONAL FEES</t>
+        </is>
+      </c>
+      <c r="C72" s="30" t="n">
+        <v>649.95</v>
+      </c>
+      <c r="D72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="30" t="n">
+        <v>9247.559999999999</v>
+      </c>
+      <c r="F72" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="28" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="28" t="n"/>
+      <c r="D73" s="28" t="n"/>
+      <c r="E73" s="28" t="n"/>
+      <c r="F73" s="28" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>7310-0000</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SUPERVISORY PAYROLL</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>7310-0005</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Supervisory Payroll Expense</t>
+        </is>
+      </c>
+      <c r="C75" s="29" t="n">
+        <v>210.99</v>
+      </c>
+      <c r="D75" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="29" t="n">
+        <v>2413.24</v>
+      </c>
+      <c r="F75" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>7310-0100</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL SUPERVISORY PAYROLL</t>
+        </is>
+      </c>
+      <c r="C76" s="36" t="n">
+        <v>210.99</v>
+      </c>
+      <c r="D76" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="36" t="n">
+        <v>2413.24</v>
+      </c>
+      <c r="F76" s="36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>7500-0000</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PAYROLL</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="n">
+        <v>210.99</v>
+      </c>
+      <c r="D77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="30" t="n">
+        <v>2413.24</v>
+      </c>
+      <c r="F77" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="28" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="31" t="n"/>
+      <c r="D78" s="31" t="n"/>
+      <c r="E78" s="31" t="n"/>
+      <c r="F78" s="31" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>7999-9000</t>
+        </is>
+      </c>
+      <c r="B79" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL NET OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C79" s="34" t="n">
+        <v>6811.46</v>
+      </c>
+      <c r="D79" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="34" t="n">
+        <v>89630.07000000001</v>
+      </c>
+      <c r="F79" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="28" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="37" t="n"/>
+      <c r="D80" s="37" t="n"/>
+      <c r="E80" s="37" t="n"/>
+      <c r="F80" s="37" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="38" t="inlineStr">
+        <is>
+          <t>7999-9999</t>
+        </is>
+      </c>
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NET OPERATING INCOME</t>
+        </is>
+      </c>
+      <c r="C81" s="40" t="n">
+        <v>4874.12</v>
+      </c>
+      <c r="D81" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="40" t="n">
+        <v>28389.43</v>
+      </c>
+      <c r="F81" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>8540-0000</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Loan Interest</t>
+        </is>
+      </c>
+      <c r="C82" s="41" t="n">
+        <v>2937.14</v>
+      </c>
+      <c r="D82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="41" t="n">
+        <v>35922.84</v>
+      </c>
+      <c r="F82" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="28" t="inlineStr">
+        <is>
+          <t>8590-0000</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL LOAN INTEREST</t>
+        </is>
+      </c>
+      <c r="C83" s="30" t="n">
+        <v>2937.14</v>
+      </c>
+      <c r="D83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="30" t="n">
+        <v>35922.84</v>
+      </c>
+      <c r="F83" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="28" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="31" t="n"/>
+      <c r="D84" s="31" t="n"/>
+      <c r="E84" s="31" t="n"/>
+      <c r="F84" s="31" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="32" t="inlineStr">
+        <is>
+          <t>8990-0000</t>
+        </is>
+      </c>
+      <c r="B85" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="C85" s="34" t="n">
+        <v>2937.14</v>
+      </c>
+      <c r="D85" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="34" t="n">
+        <v>35922.84</v>
+      </c>
+      <c r="F85" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="28" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="37" t="n"/>
+      <c r="D86" s="37" t="n"/>
+      <c r="E86" s="37" t="n"/>
+      <c r="F86" s="37" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>9090-0000</t>
+        </is>
+      </c>
+      <c r="B87" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NET INCOME</t>
+        </is>
+      </c>
+      <c r="C87" s="42" t="n">
+        <v>1936.98</v>
+      </c>
+      <c r="D87" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="42" t="n">
+        <v>-7533.41</v>
+      </c>
+      <c r="F87" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="28" t="n"/>
+      <c r="B88" s="9" t="n"/>
+      <c r="C88" s="43" t="n"/>
+      <c r="D88" s="43" t="n"/>
+      <c r="E88" s="43" t="n"/>
+      <c r="F88" s="43" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="28" t="n"/>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="28" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="28" t="n"/>
+      <c r="D90" s="28" t="n"/>
+      <c r="E90" s="28" t="n"/>
+      <c r="F90" s="28" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="28" t="inlineStr">
+        <is>
+          <t>1300-0000</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>-977</v>
+      </c>
+      <c r="D91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>-8332.23</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="28" t="inlineStr">
+        <is>
+          <t>1350-0001</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pre-Paid Insurance</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>1815.75</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="28" t="inlineStr">
+        <is>
+          <t>2110-0000</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Note 1 Principal</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="n">
+        <v>-596.53</v>
+      </c>
+      <c r="D93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>-6481.2</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>2150-0020</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Due To/(From) Other Property</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>9514.450000000001</v>
+      </c>
+      <c r="D94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>6909.8</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="28" t="inlineStr">
+        <is>
+          <t>2150-0022</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Due To/(From) SSSM</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>2650</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="28" t="inlineStr">
+        <is>
+          <t>2200-0000</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>-422.27</v>
+      </c>
+      <c r="D96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>20959.96</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>2210-0000</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Prepaid Rent</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>-218</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>-501.99</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>2305-0000</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Real Estate Tax Accrual</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>-13942.34</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>-18545.65</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>2310-0000</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sales Tax Collected</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>-73.45999999999999</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>-233.12</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>2640-0998</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Expense Accrual</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>211.06</v>
+      </c>
+      <c r="D100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>209.82</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>2640-0999</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Payroll Accrual</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>3300-0000</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Owner Distributions</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>-9638.67</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="28" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="31" t="n"/>
+      <c r="D103" s="31" t="n"/>
+      <c r="E103" s="31" t="n"/>
+      <c r="F103" s="31" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="28" t="n"/>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="C104" s="30" t="n">
+        <v>-6477.72</v>
+      </c>
+      <c r="D104" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="30" t="n">
+        <v>-11174.35</v>
+      </c>
+      <c r="F104" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="28" t="n"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="31" t="n"/>
+      <c r="D105" s="31" t="n"/>
+      <c r="E105" s="31" t="n"/>
+      <c r="F105" s="31" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="28" t="n"/>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C106" s="30" t="n">
+        <v>-4540.74</v>
+      </c>
+      <c r="D106" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="30" t="n">
+        <v>-18707.76</v>
+      </c>
+      <c r="F106" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="28" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="28" t="n"/>
+      <c r="B108" s="33" t="inlineStr">
+        <is>
+          <t>Period to Date</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="D108" s="32" t="inlineStr">
+        <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="E108" s="32" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="F108" s="28" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="28" t="inlineStr">
+        <is>
+          <t>1110-1532</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>EP NFSS Amalgamated</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="28" t="n"/>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="28" t="inlineStr">
+        <is>
+          <t>1110-4953</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>NFSS Chase</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="28" t="n"/>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="28" t="inlineStr">
+        <is>
+          <t>1110-4983</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>SMS NFSS Chase</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>1630.55</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>-2910.19</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>-4540.74</v>
+      </c>
+      <c r="F111" s="28" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="28" t="n"/>
+      <c r="B112" s="33" t="inlineStr">
+        <is>
+          <t>Total Cash</t>
+        </is>
+      </c>
+      <c r="C112" s="44" t="n">
+        <v>1630.55</v>
+      </c>
+      <c r="D112" s="44" t="n">
+        <v>-2910.19</v>
+      </c>
+      <c r="E112" s="44" t="n">
+        <v>-4540.74</v>
+      </c>
+      <c r="F112" s="28" t="n"/>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="28" t="n"/>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="28" t="n"/>
+      <c r="B114" s="33" t="inlineStr">
+        <is>
+          <t>Year to Date</t>
+        </is>
+      </c>
+      <c r="C114" s="32" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="D114" s="32" t="inlineStr">
+        <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="E114" s="32" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="F114" s="28" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="28" t="inlineStr">
+        <is>
+          <t>1110-1532</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>EP NFSS Amalgamated</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="A116" s="28" t="inlineStr">
+        <is>
+          <t>1110-4953</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>NFSS Chase</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="28" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="28" t="inlineStr">
+        <is>
+          <t>1110-4983</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>SMS NFSS Chase</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>15797.57</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>-2910.19</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>-18707.76</v>
+      </c>
+      <c r="F117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="28" t="n"/>
+      <c r="B118" s="33" t="inlineStr">
+        <is>
+          <t>Total Cash</t>
+        </is>
+      </c>
+      <c r="C118" s="44" t="n">
+        <v>15797.57</v>
+      </c>
+      <c r="D118" s="44" t="n">
+        <v>-2910.19</v>
+      </c>
+      <c r="E118" s="44" t="n">
+        <v>-18707.76</v>
+      </c>
+      <c r="F118" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>